--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112203601</v>
+        <v>112204071</v>
       </c>
       <c r="B22" t="n">
-        <v>8387</v>
+        <v>95732</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3097,32 +3097,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>221944</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3130,13 +3133,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558087</v>
+        <v>558130</v>
       </c>
       <c r="R22" t="n">
-        <v>6627982</v>
+        <v>6628068</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3180,12 +3183,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>på mossigt block</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3203,10 +3206,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112222749</v>
+        <v>112203601</v>
       </c>
       <c r="B23" t="n">
-        <v>89592</v>
+        <v>8387</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3215,30 +3218,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3246,10 +3255,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558131</v>
+        <v>558087</v>
       </c>
       <c r="R23" t="n">
-        <v>6628068</v>
+        <v>6627982</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3296,12 +3305,12 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3319,10 +3328,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112457954</v>
+        <v>112222749</v>
       </c>
       <c r="B24" t="n">
-        <v>89617</v>
+        <v>89592</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3331,25 +3340,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3358,17 +3367,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558132</v>
+        <v>558131</v>
       </c>
       <c r="R24" t="n">
-        <v>6628143</v>
+        <v>6628068</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3392,12 +3401,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3412,7 +3421,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3435,10 +3444,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112457599</v>
+        <v>112457954</v>
       </c>
       <c r="B25" t="n">
-        <v>96845</v>
+        <v>89617</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,43 +3456,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3491,10 +3487,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558038</v>
+        <v>558132</v>
       </c>
       <c r="R25" t="n">
-        <v>6628211</v>
+        <v>6628143</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,7 +3537,12 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Mossig gammal barrblandskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3559,10 +3560,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112501403</v>
+        <v>112457599</v>
       </c>
       <c r="B26" t="n">
-        <v>96853</v>
+        <v>96845</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3594,7 +3595,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3611,14 +3612,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557958</v>
+        <v>558038</v>
       </c>
       <c r="R26" t="n">
-        <v>6628535</v>
+        <v>6628211</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3645,12 +3646,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,7 +3666,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Mossig gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3683,10 +3684,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112501432</v>
+        <v>112501403</v>
       </c>
       <c r="B27" t="n">
-        <v>89625</v>
+        <v>96853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3695,30 +3696,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3726,10 +3740,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557940</v>
+        <v>557958</v>
       </c>
       <c r="R27" t="n">
-        <v>6628530</v>
+        <v>6628535</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3777,11 +3791,6 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3799,10 +3808,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112501295</v>
+        <v>112501432</v>
       </c>
       <c r="B28" t="n">
-        <v>8424</v>
+        <v>89625</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3815,32 +3824,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3848,10 +3851,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558049</v>
+        <v>557940</v>
       </c>
       <c r="R28" t="n">
-        <v>6628477</v>
+        <v>6628530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3898,12 +3901,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tallskog, inslag av unga granplantor</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3921,10 +3924,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112501340</v>
+        <v>112501295</v>
       </c>
       <c r="B29" t="n">
-        <v>90922</v>
+        <v>8424</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3937,26 +3940,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3964,10 +3973,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557994</v>
+        <v>558049</v>
       </c>
       <c r="R29" t="n">
-        <v>6628516</v>
+        <v>6628477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4014,7 +4023,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Barrblandskog, mot tallmosse</t>
+          <t>Tallskog, inslag av unga granplantor</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4032,10 +4046,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112501672</v>
+        <v>112501340</v>
       </c>
       <c r="B30" t="n">
-        <v>89625</v>
+        <v>90922</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4048,21 +4062,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4075,10 +4089,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557941</v>
+        <v>557994</v>
       </c>
       <c r="R30" t="n">
-        <v>6628426</v>
+        <v>6628516</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4125,12 +4139,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog, mot tallmosse</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4148,7 +4157,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112501410</v>
+        <v>112501672</v>
       </c>
       <c r="B31" t="n">
         <v>89625</v>
@@ -4191,10 +4200,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557958</v>
+        <v>557941</v>
       </c>
       <c r="R31" t="n">
-        <v>6628535</v>
+        <v>6628426</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4264,10 +4273,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112501658</v>
+        <v>112501410</v>
       </c>
       <c r="B32" t="n">
-        <v>96853</v>
+        <v>89625</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4276,43 +4285,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4320,10 +4316,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557921</v>
+        <v>557958</v>
       </c>
       <c r="R32" t="n">
-        <v>6628494</v>
+        <v>6628535</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4371,6 +4367,11 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4388,10 +4389,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112501637</v>
+        <v>112501658</v>
       </c>
       <c r="B33" t="n">
-        <v>90922</v>
+        <v>96853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4400,30 +4401,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4431,7 +4445,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557914</v>
+        <v>557921</v>
       </c>
       <c r="R33" t="n">
         <v>6628494</v>
@@ -4499,65 +4513,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112501817</v>
+        <v>112501637</v>
       </c>
       <c r="B34" t="n">
-        <v>56639</v>
+        <v>90922</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558037</v>
+        <v>557914</v>
       </c>
       <c r="R34" t="n">
-        <v>6628280</v>
+        <v>6628494</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4584,29 +4589,25 @@
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4623,14 +4624,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112501787</v>
+        <v>112501817</v>
       </c>
       <c r="B35" t="n">
-        <v>57414</v>
+        <v>56639</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4639,43 +4640,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558036</v>
+        <v>558037</v>
       </c>
       <c r="R35" t="n">
         <v>6628280</v>
@@ -4721,11 +4722,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>meståg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4752,14 +4748,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112837734</v>
+        <v>112501787</v>
       </c>
       <c r="B36" t="n">
-        <v>56898</v>
+        <v>57414</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4785,16 +4781,12 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4808,7 +4800,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558037</v>
+        <v>558036</v>
       </c>
       <c r="R36" t="n">
         <v>6628280</v>
@@ -4838,22 +4830,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>meståg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4877,6 +4874,134 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>112837734</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56898</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Månses hål, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>558037</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6628280</v>
+      </c>
+      <c r="S37" t="n">
+        <v>100</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73217558</v>
+        <v>112203759</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558435.4383594916</v>
+        <v>557997</v>
       </c>
       <c r="R2" t="n">
-        <v>6628367.676215677</v>
+        <v>6628183</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,43 +757,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog med lövinslag</t>
+          <t>Barrblandskog, hedartad</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>I mossa</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Bsenko</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Bsenko, Tom Sävström</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73392882</v>
+        <v>112204239</v>
       </c>
       <c r="B3" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,47 +797,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåbärsberget V, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558408.8267046907</v>
+        <v>558147</v>
       </c>
       <c r="R3" t="n">
-        <v>6628167.374970963</v>
+        <v>6627943</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +874,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gammal mossig granskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,57 +897,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73391737</v>
+        <v>112222749</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558526.7271182318</v>
+        <v>558131</v>
       </c>
       <c r="R4" t="n">
-        <v>6628110.821047795</v>
+        <v>6628068</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +965,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +985,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,62 +1008,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73391459</v>
+        <v>73392882</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Blåbärsberget V, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558244.9349804049</v>
+        <v>558409</v>
       </c>
       <c r="R5" t="n">
-        <v>6628004.690523252</v>
+        <v>6628167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,19 +1086,9 @@
           <t>2018-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1103,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gammal mossig granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1177,62 +1121,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73394045</v>
+        <v>112163592</v>
       </c>
       <c r="B6" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåbärsberget V, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558373.3498710629</v>
+        <v>558062</v>
       </c>
       <c r="R6" t="n">
-        <v>6628146.174837617</v>
+        <v>6628273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,22 +1197,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>i bestånd med gamla granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1222,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1307,15 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98358713</v>
+        <v>112163912</v>
       </c>
       <c r="B7" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,46 +1251,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenramen, Ramnäs sn, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558096.7493127903</v>
+        <v>558020</v>
       </c>
       <c r="R7" t="n">
-        <v>6627868.939412979</v>
+        <v>6628293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,27 +1308,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 ex hoppat omkring i vägslänten och betat björkknopp</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,79 +1322,88 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog, renlavsmarker</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Däggdjursinventering Surahammar</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109873621</v>
+        <v>112163316</v>
       </c>
       <c r="B8" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Källdalen SV, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558204.8449591948</v>
+        <v>558054</v>
       </c>
       <c r="R8" t="n">
-        <v>6628600.685923523</v>
+        <v>6628665</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,22 +1427,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tätt bestånd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,7 +1452,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,62 +1470,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109873645</v>
+        <v>112163367</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källdalsmossen V, Vstm</t>
+          <t>Källdalen SV, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558204.8449591948</v>
+        <v>558083</v>
       </c>
       <c r="R9" t="n">
-        <v>6628600.685923523</v>
+        <v>6628612</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,22 +1538,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,12 +1558,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrblandskog, lövinslag</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1694,15 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112163592</v>
+        <v>112163866</v>
       </c>
       <c r="B10" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,33 +1587,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1745,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558062</v>
+        <v>558020</v>
       </c>
       <c r="R10" t="n">
-        <v>6628273</v>
+        <v>6628293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1783,11 +1652,6 @@
           <t>2023-09-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>i bestånd med gamla granar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1800,7 +1664,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Gammal barrblandskog, renlavsmarker</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1821,16 +1685,11 @@
         <v>112164162</v>
       </c>
       <c r="B11" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1861,7 +1720,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558022</v>
+        <v>558023</v>
       </c>
       <c r="R11" t="n">
         <v>6628310</v>
@@ -1929,19 +1788,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112163316</v>
+        <v>112203716</v>
       </c>
       <c r="B12" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1962,31 +1816,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källdalen SV, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558054</v>
+        <v>558021</v>
       </c>
       <c r="R12" t="n">
-        <v>6628665</v>
+        <v>6628143</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2010,17 +1856,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tätt bestånd.</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2035,7 +1876,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog, hedartad</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2053,15 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112163912</v>
+        <v>112501340</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2069,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2092,14 +1928,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558020</v>
+        <v>557994</v>
       </c>
       <c r="R13" t="n">
-        <v>6628293</v>
+        <v>6628516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2126,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2146,12 +1982,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, renlavsmarker</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog, mot tallmosse</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2169,19 +2000,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112163367</v>
+        <v>112501637</v>
       </c>
       <c r="B14" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2208,14 +2034,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källdalen SV, Vstm</t>
+          <t>Månses hål N, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558083</v>
+        <v>557914</v>
       </c>
       <c r="R14" t="n">
-        <v>6628611</v>
+        <v>6628494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2242,12 +2068,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,7 +2088,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2280,15 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112164196</v>
+        <v>73217601</v>
       </c>
       <c r="B15" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,45 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4404</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558007</v>
+        <v>558433</v>
       </c>
       <c r="R15" t="n">
-        <v>6628378</v>
+        <v>6628415</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,12 +2171,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,80 +2185,78 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, renlavsmarker</t>
+          <t>Barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>I mossa</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko, Tom Sävström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112163866</v>
+        <v>73390701</v>
       </c>
       <c r="B16" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4404</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558020</v>
+        <v>558147</v>
       </c>
       <c r="R16" t="n">
-        <v>6628293</v>
+        <v>6627892</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,12 +2280,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,7 +2300,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, renlavsmarker</t>
+          <t>Äldre blandskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2510,54 +2318,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112164100</v>
+        <v>73391648</v>
       </c>
       <c r="B17" t="n">
-        <v>95746</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>4404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558020</v>
+        <v>558245</v>
       </c>
       <c r="R17" t="n">
-        <v>6628293</v>
+        <v>6628005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2584,12 +2385,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,7 +2405,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2622,15 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112204239</v>
+        <v>73392912</v>
       </c>
       <c r="B18" t="n">
-        <v>89592</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,40 +2434,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>4404</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blåbärsberget SV, Vstm</t>
+          <t>Blåbärsberget V, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558147</v>
+        <v>558373</v>
       </c>
       <c r="R18" t="n">
-        <v>6627943</v>
+        <v>6628146</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2695,12 +2490,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2510,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal mossig granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2738,15 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112203759</v>
+        <v>112163539</v>
       </c>
       <c r="B19" t="n">
-        <v>89592</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2754,21 +2539,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4404</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2777,17 +2562,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Månses hål S, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557997</v>
+        <v>558062</v>
       </c>
       <c r="R19" t="n">
-        <v>6628183</v>
+        <v>6628273</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,12 +2596,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,18 +2610,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Barrblandskog, hedartad</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2854,37 +2633,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112203716</v>
+        <v>112203574</v>
       </c>
       <c r="B20" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4404</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2897,13 +2671,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558021</v>
+        <v>558087</v>
       </c>
       <c r="R20" t="n">
-        <v>6628143</v>
+        <v>6627982</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2947,7 +2721,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrblandskog, hedartad</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2965,37 +2739,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112204109</v>
+        <v>112203619</v>
       </c>
       <c r="B21" t="n">
-        <v>89556</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>4404</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3008,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558126</v>
+        <v>558110</v>
       </c>
       <c r="R21" t="n">
-        <v>6627991</v>
+        <v>6628072</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3058,12 +2827,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3081,51 +2845,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112204071</v>
+        <v>112203857</v>
       </c>
       <c r="B22" t="n">
-        <v>95732</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221944</v>
+        <v>4404</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3133,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558130</v>
+        <v>558057</v>
       </c>
       <c r="R22" t="n">
-        <v>6628068</v>
+        <v>6628192</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3183,12 +2933,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>på mossigt block</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3206,48 +2951,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112203601</v>
+        <v>112203881</v>
       </c>
       <c r="B23" t="n">
-        <v>8387</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>4404</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3255,13 +2989,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558087</v>
+        <v>558101</v>
       </c>
       <c r="R23" t="n">
-        <v>6627982</v>
+        <v>6628163</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3306,11 +3040,6 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3328,53 +3057,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112222749</v>
+        <v>73391573</v>
       </c>
       <c r="B24" t="n">
-        <v>89592</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Månses hål S, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558131</v>
+        <v>558259</v>
       </c>
       <c r="R24" t="n">
-        <v>6628068</v>
+        <v>6627996</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3401,12 +3124,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3421,12 +3144,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3444,15 +3162,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112457954</v>
+        <v>73391603</v>
       </c>
       <c r="B25" t="n">
-        <v>89617</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,20 +3193,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Blåbärsberget SV, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558132</v>
+        <v>558259</v>
       </c>
       <c r="R25" t="n">
-        <v>6628143</v>
+        <v>6627996</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3517,12 +3229,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3537,7 +3249,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3560,69 +3272,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112457599</v>
+        <v>112204109</v>
       </c>
       <c r="B26" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558038</v>
+        <v>558126</v>
       </c>
       <c r="R26" t="n">
-        <v>6628211</v>
+        <v>6627991</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3646,12 +3340,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3666,7 +3360,12 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Mossig gammal barrblandskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3684,66 +3383,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112501403</v>
+        <v>112457954</v>
       </c>
       <c r="B27" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557958</v>
+        <v>558133</v>
       </c>
       <c r="R27" t="n">
-        <v>6628535</v>
+        <v>6628143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3770,12 +3451,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3791,6 +3472,11 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3808,15 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112501432</v>
+        <v>112501410</v>
       </c>
       <c r="B28" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3851,10 +3532,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557940</v>
+        <v>557958</v>
       </c>
       <c r="R28" t="n">
-        <v>6628530</v>
+        <v>6628535</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3924,15 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112501295</v>
+        <v>112501432</v>
       </c>
       <c r="B29" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3940,32 +3616,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3973,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558049</v>
+        <v>557940</v>
       </c>
       <c r="R29" t="n">
-        <v>6628477</v>
+        <v>6628530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4023,12 +3693,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Tallskog, inslag av unga granplantor</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4046,15 +3716,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112501340</v>
+        <v>112501672</v>
       </c>
       <c r="B30" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4062,21 +3727,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4089,10 +3754,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557994</v>
+        <v>557941</v>
       </c>
       <c r="R30" t="n">
-        <v>6628516</v>
+        <v>6628426</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4139,7 +3804,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrblandskog, mot tallmosse</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4157,53 +3827,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112501672</v>
+        <v>73217558</v>
       </c>
       <c r="B31" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557941</v>
+        <v>558435</v>
       </c>
       <c r="R31" t="n">
-        <v>6628426</v>
+        <v>6628368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4230,12 +3892,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4244,82 +3906,84 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog med lövinslag</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>I mossa</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Lars Bsenko, Tom Sävström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112501410</v>
+        <v>112164196</v>
       </c>
       <c r="B32" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557958</v>
+        <v>558007</v>
       </c>
       <c r="R32" t="n">
-        <v>6628535</v>
+        <v>6628377</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4346,12 +4010,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4366,12 +4030,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Gammal barrblandskog, renlavsmarker</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4389,69 +4048,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112501658</v>
+        <v>112203677</v>
       </c>
       <c r="B33" t="n">
-        <v>96853</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557921</v>
+        <v>558040</v>
       </c>
       <c r="R33" t="n">
-        <v>6628494</v>
+        <v>6628055</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4475,12 +4124,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4495,7 +4144,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, hedartad</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4513,15 +4162,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112501637</v>
+        <v>126260723</v>
       </c>
       <c r="B34" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,40 +4173,53 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Månses hål N, Vstm</t>
+          <t>Månses hål , Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557914</v>
+        <v>558085</v>
       </c>
       <c r="R34" t="n">
-        <v>6628494</v>
+        <v>6628591</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4586,12 +4243,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Flög in mot Ulvsbomurens NR</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4600,56 +4272,45 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112501817</v>
+        <v>108679001</v>
       </c>
       <c r="B35" t="n">
-        <v>56639</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4659,14 +4320,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4676,13 +4337,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558037</v>
+        <v>558109</v>
       </c>
       <c r="R35" t="n">
-        <v>6628280</v>
+        <v>6628274</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4706,22 +4367,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4748,65 +4409,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112501787</v>
+        <v>109873645</v>
       </c>
       <c r="B36" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Källdalsmossen V, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558036</v>
+        <v>558205</v>
       </c>
       <c r="R36" t="n">
-        <v>6628280</v>
+        <v>6628601</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4830,27 +4483,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>meståg</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4859,8 +4507,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrblandskog, lövinslag</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4877,69 +4536,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112837734</v>
+        <v>112203601</v>
       </c>
       <c r="B37" t="n">
-        <v>56898</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Månses hål, Vstm</t>
+          <t>Månses hål S, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558037</v>
+        <v>558087</v>
       </c>
       <c r="R37" t="n">
-        <v>6628280</v>
+        <v>6627982</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4963,22 +4610,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4987,8 +4624,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5002,6 +4650,1499 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>112501295</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Månses hål N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>558049</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6628477</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Tallskog, inslag av unga granplantor</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>98358713</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stenramen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>558097</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6627869</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-01-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 ex hoppat omkring i vägslänten och betat björkknopp</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Däggdjursinventering Surahammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>112457599</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Månses hål, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>558038</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6628211</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Mossig gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112501403</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Månses hål N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>557958</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6628535</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112501658</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Månses hål N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>557921</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6628494</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>73394045</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Blåbärsberget V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>558373</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6628146</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>73391459</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Blåbärsberget SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>558245</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6628005</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>112164100</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Månses hål, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>558020</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6628293</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>112204071</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Månses hål S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>558130</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6628068</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>på mossigt block</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>109873621</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Källdalsmossen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>558205</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6628601</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Barrblandskog, lövinslag</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>73391737</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Blåbärsberget SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>558527</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6628111</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>100803900</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Blåbärsberget V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>558564</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6628255</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-05-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-05-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lise-Lotte Norin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124519006</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kölberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>558532</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6628372</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34759-2023 artfynd.xlsx
+++ b/artfynd/A 34759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112222749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392882</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112163592</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112163912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112163316</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112163367</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112163866</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164162</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203716</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501340</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2103,6 +2168,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501637</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2210,6 +2280,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73217601</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73390701</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2420,6 +2500,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73391648</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2525,6 +2610,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392912</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2630,6 +2720,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112163539</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2736,6 +2831,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203574</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2842,6 +2942,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203619</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2948,6 +3053,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203857</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3054,6 +3164,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203881</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3159,6 +3274,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73391573</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3269,6 +3389,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73391603</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3380,6 +3505,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204109</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3491,6 +3621,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112457954</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3602,6 +3737,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501410</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3713,6 +3853,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501432</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3824,6 +3969,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501672</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3931,6 +4081,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73217558</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4045,6 +4200,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164196</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4159,6 +4319,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203677</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4287,6 +4452,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126260723</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4406,6 +4576,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108679001</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4533,6 +4708,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109873645</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4650,6 +4830,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112203601</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4767,6 +4952,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501295</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4895,6 +5085,11 @@
           <t>Däggdjursinventering Surahammar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98358713</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5014,6 +5209,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112457599</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5133,6 +5333,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501403</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5252,6 +5457,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112501658</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5367,6 +5577,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73394045</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5482,6 +5697,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73391459</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5589,6 +5809,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112164100</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5705,6 +5930,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204071</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5812,6 +6042,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73391737</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5919,6 +6154,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100803900</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6036,6 +6276,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109873621</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6143,8 +6388,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124519006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>